--- a/demo.xlsx
+++ b/demo.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,35 +454,25 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Curso Académico</t>
+          <t>Tipo de Entrada</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tipo de Entrada</t>
+          <t>Título/Asunto</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Título/Asunto</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Enlace a documento (subir pdf)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>Profesional que registra</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Enlace a documento (subir pdf)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
@@ -511,29 +501,27 @@
       <c r="F2" t="n">
         <v>10001</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Reunión con tutora del IES</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Reunión con tutora del IES</t>
+          <t>Coordinación de pautas de apoyo en aula. Compromiso de revisión en 15 días.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Coordinación de pautas de apoyo en aula. Compromiso de revisión en 15 días.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -558,25 +546,23 @@
       <c r="F3" t="n">
         <v>10001</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Llamada a familia</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Llamada a familia</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>Se informa a la madre del avance en autocontrol y se acuerda nueva cita.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Familia receptiva</t>
         </is>
@@ -605,25 +591,23 @@
       <c r="F4" t="n">
         <v>10001</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Adaptación metodológica</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Adaptación metodológica</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>Se acuerda permitir descansos cortos durante las clases largas.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -648,29 +632,27 @@
       <c r="F5" t="n">
         <v>10001</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe de evaluación inicial</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Informe de evaluación inicial</t>
+          <t>Documento entregado al equipo docente con perfil y necesidades.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Documento entregado al equipo docente con perfil y necesidades.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -695,25 +677,23 @@
       <c r="F6" t="n">
         <v>10002</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Reunión con logopeda externo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Reunión con logopeda externo</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>Puesta en común de estrategias de lectoescritura aplicadas en lenguaje musical.</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -738,25 +718,23 @@
       <c r="F7" t="n">
         <v>10002</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Reunión con familia</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Reunión con familia</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>Información sobre evolución del trimestre y materiales adaptados.</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -781,29 +759,27 @@
       <c r="F8" t="n">
         <v>10002</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe inicial de dislexia</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Informe inicial de dislexia</t>
+          <t>Recopilación de antecedentes y recomendaciones del logopeda.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Recopilación de antecedentes y recomendaciones del logopeda.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -828,25 +804,23 @@
       <c r="F9" t="n">
         <v>10003</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Pausar seguimiento</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pausar seguimiento</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>Se decide pausar el seguimiento tras evolución estable.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>A revisar en 6 meses</t>
         </is>
@@ -875,25 +849,23 @@
       <c r="F10" t="n">
         <v>10003</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Reunión con tutora externa</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Reunión con tutora externa</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
           <t>Intercambio de información con su tutora del centro de referencia.</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -918,25 +890,23 @@
       <c r="F11" t="n">
         <v>10004</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Cierre de caso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cierre de caso</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>Adaptación satisfactoria al grupo. Se cierra el seguimiento activo.</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -961,29 +931,27 @@
       <c r="F12" t="n">
         <v>10005</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Suceso</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Suceso</t>
+          <t>Episodio de bloqueo en examen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Episodio de bloqueo en examen</t>
+          <t>Crisis de ansiedad durante la prueba trimestral. Se acompaña y se contacta con familia.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Crisis de ansiedad durante la prueba trimestral. Se acompaña y se contacta con familia.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1008,25 +976,23 @@
       <c r="F13" t="n">
         <v>10005</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Reunión con madre</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Reunión con madre</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>Acuerdos sobre rutinas en casa antes de las pruebas.</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1051,29 +1017,27 @@
       <c r="F14" t="n">
         <v>10005</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Derivación</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Derivación</t>
+          <t>Derivación a psicóloga externa</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Derivación a psicóloga externa</t>
+          <t>Se sugiere a la familia consulta con profesional especializado.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Se sugiere a la familia consulta con profesional especializado.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1098,29 +1062,27 @@
       <c r="F15" t="n">
         <v>10005</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe de seguimiento</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Informe de seguimiento</t>
+          <t>Documento resumen del primer trimestre.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Documento resumen del primer trimestre.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1145,25 +1107,23 @@
       <c r="F16" t="n">
         <v>10005</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Reunión inicial con tutora</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Reunión inicial con tutora</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>Presentación del caso y necesidades del alumno.</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1188,25 +1148,23 @@
       <c r="F17" t="n">
         <v>10006</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Programa de enriquecimiento</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Programa de enriquecimiento</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
           <t>Se acuerda repertorio adicional y proyecto personal.</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1231,25 +1189,23 @@
       <c r="F18" t="n">
         <v>10006</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Coordinación con instituto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Coordinación con instituto</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
           <t>Reunión con orientadora del IES para complementar plan.</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1274,25 +1230,23 @@
       <c r="F19" t="n">
         <v>10007</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Llamada a madre</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Llamada a madre</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
           <t>Información sobre próxima cita con psicóloga externa.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1317,29 +1271,27 @@
       <c r="F20" t="n">
         <v>10007</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Suceso</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Suceso</t>
+          <t>Bloqueo en audición</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bloqueo en audición</t>
+          <t>Episodio de ansiedad durante audición. Se acompaña.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Episodio de ansiedad durante audición. Se acompaña.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1364,29 +1316,27 @@
       <c r="F21" t="n">
         <v>10007</v>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe de evaluación</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Informe de evaluación</t>
+          <t>Resumen del primer trimestre.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Resumen del primer trimestre.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1411,25 +1361,23 @@
       <c r="F22" t="n">
         <v>10008</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Pausar seguimiento</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pausar seguimiento</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
           <t>Sin necesidades urgentes. Se mantiene observación.</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1454,25 +1402,23 @@
       <c r="F23" t="n">
         <v>10009</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Reunión con familia</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Reunión con familia</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
           <t>Repaso de adaptaciones. Familia colaboradora.</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1497,29 +1443,27 @@
       <c r="F24" t="n">
         <v>10009</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Adaptación de partituras</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Adaptación de partituras</t>
+          <t>Se proporcionan materiales con tipografía y espaciado adaptados.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Se proporcionan materiales con tipografía y espaciado adaptados.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1544,29 +1488,27 @@
       <c r="F25" t="n">
         <v>10009</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe de necesidades</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Informe de necesidades</t>
+          <t>Recopilación de adaptaciones aplicadas.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Recopilación de adaptaciones aplicadas.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1591,25 +1533,23 @@
       <c r="F26" t="n">
         <v>10010</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Tutoría de orientación académica</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tutoría de orientación académica</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
           <t>Información sobre Conservatorio Superior y plazos.</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1634,25 +1574,23 @@
       <c r="F27" t="n">
         <v>10010</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Reunión informativa</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Reunión informativa</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
           <t>Resolución de dudas sobre pruebas de acceso.</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1677,29 +1615,27 @@
       <c r="F28" t="n">
         <v>10010</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Plan de preparación</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Plan de preparación</t>
+          <t>Calendario de simulacros y materiales de apoyo.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Calendario de simulacros y materiales de apoyo.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1724,25 +1660,23 @@
       <c r="F29" t="n">
         <v>10010</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Inicio del seguimiento</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Inicio del seguimiento</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
           <t>Primera entrevista del curso.</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1767,25 +1701,23 @@
       <c r="F30" t="n">
         <v>10011</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Reunión con madre</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Reunión con madre</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
           <t>Coordinación de pautas en casa.</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1810,25 +1742,23 @@
       <c r="F31" t="n">
         <v>10011</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Coordinación con tutora externa</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Coordinación con tutora externa</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
           <t>Intercambio de estrategias con tutora del centro de referencia.</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1853,25 +1783,23 @@
       <c r="F32" t="n">
         <v>10012</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Pausar seguimiento</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Pausar seguimiento</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
           <t>Caso pausado tras estabilización.</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1896,25 +1824,23 @@
       <c r="F33" t="n">
         <v>10013</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Acogida inicial</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Acogida inicial</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
           <t>Primera entrevista con la familia y la alumna.</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1939,25 +1865,23 @@
       <c r="F34" t="n">
         <v>10013</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Comunicación familia</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Comunicación familia</t>
+          <t>Llamada de seguimiento</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Llamada de seguimiento</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
           <t>Familia satisfecha con la integración.</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1982,25 +1906,23 @@
       <c r="F35" t="n">
         <v>10013</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Visita guiada al centro</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Visita guiada al centro</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
           <t>Acompañamiento durante los primeros días.</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2025,29 +1947,27 @@
       <c r="F36" t="n">
         <v>10015</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Reunión</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reunión</t>
+          <t>Coordinación con orientadora del IES</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Coordinación con orientadora del IES</t>
+          <t>Reunión telemática para alinear adaptaciones.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Reunión telemática para alinear adaptaciones.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2072,29 +1992,27 @@
       <c r="F37" t="n">
         <v>10015</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Adaptaciones metodológicas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Adaptaciones metodológicas</t>
+          <t>Material visual estructurado para clases colectivas.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Material visual estructurado para clases colectivas.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2119,29 +2037,27 @@
       <c r="F38" t="n">
         <v>10015</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Informe</t>
+          <t>Informe inicial</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Informe inicial</t>
+          <t>Recopilación de necesidades y antecedentes.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Recopilación de necesidades y antecedentes.</t>
+          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://gvaedu-my.sharepoint.com/personal/orientacion/Documents/Apps/Microsoft%20Forms/Registro/Adjuntos/ejemplo.pdf</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/demo.xlsx
+++ b/demo.xlsx
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>TEA leve</t>
+          <t>TEA</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3808,12 +3808,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Necesidades específicas de apoyo educativo</t>
+          <t>Necesidades de apoyo</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>Justificación y orientaciones</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Centro Docente</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3861,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Alumna con TDAH que necesita adaptaciones en la gestión del tiempo, descansos pautados y refuerzo de la lectura musical.</t>
+          <t>TDAH: Déficit de atención</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Se recomienda fragmentar las tareas, usar señales visuales y coordinar con la tutora del IES para mantener las mismas estrategias.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IES Joanot Martorell</t>
         </is>
       </c>
     </row>
@@ -3904,12 +3914,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Alumna con TDAH y ansiedad que requiere adaptación de las condiciones de evaluación, apoyo emocional continuado y coordinación con profesional externo.</t>
+          <t>TDAH: Combinado</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Se aconseja permitir evaluaciones en entorno controlado, avisar con antelación de las audiciones y mantener comunicación regular con la familia.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IES Joanot Martorell</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3967,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Se mantienen las necesidades del primer informe. Se añade la necesidad de un plan gradual de exposición a situaciones de interpretación pública.</t>
+          <t>TDAH: Combinado ¶ Trastorno mental grave</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Continuar con el protocolo de evaluación adaptada. Iniciar exposición progresiva a audiciones (primero en grupo, luego individual). Coordinación trimestral con la psicóloga externa.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IES Joanot Martorell</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4020,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Alumna con dislexia y ansiedad asociada que necesita materiales adaptados (tipografía, espaciado, colores) y metodología centrada en lo auditivo-práctico.</t>
+          <t>DEA: Lectura</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Proporcionar partituras con tipografía OpenDyslexic, ampliar los plazos de entrega y priorizar la evaluación práctica sobre la escrita.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IES Les Moreres</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4073,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Alumna con TEA leve que requiere anticipación de cambios, instrucciones explícitas y material visual de apoyo.</t>
+          <t>TEA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Usar apoyos visuales (horarios, secuencias), anticipar los cambios de actividad con al menos 5 minutos, y coordinar con la orientadora del IES las adaptaciones.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Col·legi La Pureza</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4126,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Alumno/a con necesidades de apoyo por situación sociofamiliar compleja. ¶ Requiere flexibilización horaria y seguimiento de asistencia.</t>
+          <t>Desventaja socioeconómica ¶ Incorporación tardía</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Coordinar con servicios sociales. ¶ Permitir asistencia flexible y facilitar materiales para trabajo autónomo.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IES Pere Boïl</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4179,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Alumno con dislexia que necesita adaptaciones en la presentación del material escrito y evaluación preferentemente oral o práctica.</t>
+          <t>DEA: Lectura</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Ampliar tiempos de lectura, usar partituras con mayor espaciado y facilitar grabaciones de audio como complemento al material escrito.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>IES Pere Boil</t>
         </is>
       </c>
     </row>
